--- a/스마트점핑_DB.xlsx
+++ b/스마트점핑_DB.xlsx
@@ -13,6 +13,8 @@
     <sheet name="textbooks" sheetId="8" r:id="rId8"/>
     <sheet name="playlists" sheetId="9" r:id="rId9"/>
     <sheet name="favorites" sheetId="10" r:id="rId10"/>
+    <sheet name="devices" sheetId="11" r:id="rId11"/>
+    <sheet name="loginlog" sheetId="12" r:id="rId12"/>
   </sheets>
 </workbook>
 </file>
@@ -406,7 +408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -833,25 +835,25 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>C5</v>
+        <v>C4</v>
       </c>
       <c r="B19" t="str">
-        <v>비트 트레이닝</v>
+        <v>스마트점핑</v>
       </c>
       <c r="C19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D19" t="str">
-        <v>S51</v>
+        <v>S47</v>
       </c>
       <c r="E19" t="str">
-        <v>동요 율동</v>
+        <v>스마트점프 초급</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G19" t="str">
-        <v/>
+        <v>N</v>
       </c>
     </row>
     <row r="20">
@@ -865,13 +867,13 @@
         <v>5</v>
       </c>
       <c r="D20" t="str">
-        <v>S52</v>
+        <v>S51</v>
       </c>
       <c r="E20" t="str">
-        <v>체조 메들리</v>
+        <v>동요 율동</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -888,39 +890,39 @@
         <v>5</v>
       </c>
       <c r="D21" t="str">
-        <v>S53</v>
+        <v>S52</v>
       </c>
       <c r="E21" t="str">
-        <v>K-POP 키즈댄스</v>
+        <v>체조 메들리</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G21" t="str">
-        <v>N</v>
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>C6</v>
+        <v>C5</v>
       </c>
       <c r="B22" t="str">
-        <v>Killing Time Zone</v>
+        <v>비트 트레이닝</v>
       </c>
       <c r="C22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D22" t="str">
-        <v>S61</v>
+        <v>S53</v>
       </c>
       <c r="E22" t="str">
-        <v>나라별 국기맞추기</v>
+        <v>K-POP 키즈댄스</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G22" t="str">
-        <v/>
+        <v>N</v>
       </c>
     </row>
     <row r="23">
@@ -934,16 +936,16 @@
         <v>6</v>
       </c>
       <c r="D23" t="str">
-        <v>S62</v>
+        <v>S61</v>
       </c>
       <c r="E23" t="str">
-        <v>숨은그림 · 틀린그림 찾기</v>
+        <v>나라별 국기맞추기</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" t="str">
-        <v>N</v>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -957,21 +959,44 @@
         <v>6</v>
       </c>
       <c r="D24" t="str">
-        <v>S63</v>
+        <v>S62</v>
       </c>
       <c r="E24" t="str">
-        <v>넌센스 퀴즈</v>
+        <v>숨은그림 · 틀린그림 찾기</v>
       </c>
       <c r="F24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G24" t="str">
         <v>N</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>C6</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Killing Time Zone</v>
+      </c>
+      <c r="C25">
+        <v>6</v>
+      </c>
+      <c r="D25" t="str">
+        <v>S63</v>
+      </c>
+      <c r="E25" t="str">
+        <v>넌센스 퀴즈</v>
+      </c>
+      <c r="F25">
+        <v>3</v>
+      </c>
+      <c r="G25" t="str">
+        <v>N</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G24"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G25"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1004,7 +1029,7 @@
         <v>V0008,V0016,V0030,V0062,V0085</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-08-22 17:23:49</v>
+        <v>2026-09-10 08:32:14</v>
       </c>
     </row>
   </sheetData>
@@ -1014,9 +1039,91 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G1"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>소유자</v>
+      </c>
+      <c r="B1" t="str">
+        <v>기기ID</v>
+      </c>
+      <c r="C1" t="str">
+        <v>기기별명</v>
+      </c>
+      <c r="D1" t="str">
+        <v>브라우저</v>
+      </c>
+      <c r="E1" t="str">
+        <v>등록일</v>
+      </c>
+      <c r="F1" t="str">
+        <v>최근접속</v>
+      </c>
+      <c r="G1" t="str">
+        <v>상태</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F1"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>시각</v>
+      </c>
+      <c r="B1" t="str">
+        <v>아이디</v>
+      </c>
+      <c r="C1" t="str">
+        <v>기기ID</v>
+      </c>
+      <c r="D1" t="str">
+        <v>학교코드</v>
+      </c>
+      <c r="E1" t="str">
+        <v>결과</v>
+      </c>
+      <c r="F1" t="str">
+        <v>비고</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I105"/>
+  <dimension ref="A1:J107"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -1027,6 +1134,7 @@
     <col min="7" max="7" width="12.83203125" customWidth="1"/>
     <col min="8" max="8" width="12.83203125" customWidth="1"/>
     <col min="9" max="9" width="12.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1057,6 +1165,9 @@
       <c r="I1" t="str">
         <v>노출여부</v>
       </c>
+      <c r="J1" t="str">
+        <v>등록자</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -1081,10 +1192,13 @@
         <v>1091</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I2" t="str">
         <v>Y</v>
+      </c>
+      <c r="J2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -1110,10 +1224,13 @@
         <v>2062</v>
       </c>
       <c r="H3" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I3" t="str">
         <v>Y</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -1139,10 +1256,13 @@
         <v>3033</v>
       </c>
       <c r="H4" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I4" t="str">
         <v>Y</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -1168,10 +1288,13 @@
         <v>4004</v>
       </c>
       <c r="H5" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I5" t="str">
         <v>Y</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -1197,10 +1320,13 @@
         <v>4975</v>
       </c>
       <c r="H6" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I6" t="str">
         <v>Y</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -1226,10 +1352,13 @@
         <v>5946</v>
       </c>
       <c r="H7" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I7" t="str">
         <v>Y</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -1255,10 +1384,13 @@
         <v>6917</v>
       </c>
       <c r="H8" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I8" t="str">
         <v>Y</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -1284,10 +1416,13 @@
         <v>7888</v>
       </c>
       <c r="H9" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I9" t="str">
         <v>Y</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -1313,10 +1448,13 @@
         <v>8859</v>
       </c>
       <c r="H10" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I10" t="str">
         <v>Y</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -1342,10 +1480,13 @@
         <v>430</v>
       </c>
       <c r="H11" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I11" t="str">
         <v>Y</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -1371,10 +1512,13 @@
         <v>1401</v>
       </c>
       <c r="H12" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I12" t="str">
         <v>Y</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -1400,10 +1544,13 @@
         <v>2372</v>
       </c>
       <c r="H13" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I13" t="str">
         <v>Y</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -1429,10 +1576,13 @@
         <v>3343</v>
       </c>
       <c r="H14" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I14" t="str">
         <v>Y</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1458,10 +1608,13 @@
         <v>4314</v>
       </c>
       <c r="H15" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I15" t="str">
         <v>Y</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -1487,10 +1640,13 @@
         <v>5285</v>
       </c>
       <c r="H16" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I16" t="str">
         <v>Y</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -1516,10 +1672,13 @@
         <v>6256</v>
       </c>
       <c r="H17" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I17" t="str">
         <v>Y</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -1545,10 +1704,13 @@
         <v>7227</v>
       </c>
       <c r="H18" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I18" t="str">
         <v>Y</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1574,10 +1736,13 @@
         <v>8198</v>
       </c>
       <c r="H19" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I19" t="str">
         <v>Y</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -1603,10 +1768,13 @@
         <v>9169</v>
       </c>
       <c r="H20" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I20" t="str">
         <v>Y</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -1632,10 +1800,13 @@
         <v>740</v>
       </c>
       <c r="H21" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I21" t="str">
         <v>Y</v>
+      </c>
+      <c r="J21" t="str">
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -1661,10 +1832,13 @@
         <v>1711</v>
       </c>
       <c r="H22" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I22" t="str">
         <v>Y</v>
+      </c>
+      <c r="J22" t="str">
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -1690,10 +1864,13 @@
         <v>2682</v>
       </c>
       <c r="H23" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I23" t="str">
         <v>Y</v>
+      </c>
+      <c r="J23" t="str">
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -1719,10 +1896,13 @@
         <v>3653</v>
       </c>
       <c r="H24" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I24" t="str">
         <v>Y</v>
+      </c>
+      <c r="J24" t="str">
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -1748,10 +1928,13 @@
         <v>4624</v>
       </c>
       <c r="H25" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I25" t="str">
         <v>Y</v>
+      </c>
+      <c r="J25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -1777,10 +1960,13 @@
         <v>5595</v>
       </c>
       <c r="H26" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I26" t="str">
         <v>Y</v>
+      </c>
+      <c r="J26" t="str">
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -1806,10 +1992,13 @@
         <v>6566</v>
       </c>
       <c r="H27" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I27" t="str">
         <v>Y</v>
+      </c>
+      <c r="J27" t="str">
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -1835,10 +2024,13 @@
         <v>7537</v>
       </c>
       <c r="H28" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I28" t="str">
         <v>Y</v>
+      </c>
+      <c r="J28" t="str">
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -1864,10 +2056,13 @@
         <v>8508</v>
       </c>
       <c r="H29" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I29" t="str">
         <v>Y</v>
+      </c>
+      <c r="J29" t="str">
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -1893,10 +2088,13 @@
         <v>9479</v>
       </c>
       <c r="H30" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I30" t="str">
         <v>Y</v>
+      </c>
+      <c r="J30" t="str">
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -1922,10 +2120,13 @@
         <v>1050</v>
       </c>
       <c r="H31" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I31" t="str">
         <v>Y</v>
+      </c>
+      <c r="J31" t="str">
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -1951,10 +2152,13 @@
         <v>2021</v>
       </c>
       <c r="H32" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I32" t="str">
         <v>Y</v>
+      </c>
+      <c r="J32" t="str">
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -1980,10 +2184,13 @@
         <v>2992</v>
       </c>
       <c r="H33" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I33" t="str">
         <v>Y</v>
+      </c>
+      <c r="J33" t="str">
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -2009,10 +2216,13 @@
         <v>3963</v>
       </c>
       <c r="H34" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I34" t="str">
         <v>Y</v>
+      </c>
+      <c r="J34" t="str">
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -2038,10 +2248,13 @@
         <v>4934</v>
       </c>
       <c r="H35" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I35" t="str">
         <v>Y</v>
+      </c>
+      <c r="J35" t="str">
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -2067,10 +2280,13 @@
         <v>5905</v>
       </c>
       <c r="H36" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I36" t="str">
         <v>Y</v>
+      </c>
+      <c r="J36" t="str">
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -2096,10 +2312,13 @@
         <v>6876</v>
       </c>
       <c r="H37" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I37" t="str">
         <v>Y</v>
+      </c>
+      <c r="J37" t="str">
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -2125,10 +2344,13 @@
         <v>7847</v>
       </c>
       <c r="H38" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I38" t="str">
         <v>Y</v>
+      </c>
+      <c r="J38" t="str">
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -2154,10 +2376,13 @@
         <v>8818</v>
       </c>
       <c r="H39" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I39" t="str">
         <v>Y</v>
+      </c>
+      <c r="J39" t="str">
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -2183,10 +2408,13 @@
         <v>389</v>
       </c>
       <c r="H40" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I40" t="str">
         <v>Y</v>
+      </c>
+      <c r="J40" t="str">
+        <v/>
       </c>
     </row>
     <row r="41">
@@ -2212,10 +2440,13 @@
         <v>1360</v>
       </c>
       <c r="H41" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I41" t="str">
         <v>Y</v>
+      </c>
+      <c r="J41" t="str">
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -2241,10 +2472,13 @@
         <v>2331</v>
       </c>
       <c r="H42" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I42" t="str">
         <v>Y</v>
+      </c>
+      <c r="J42" t="str">
+        <v/>
       </c>
     </row>
     <row r="43">
@@ -2270,10 +2504,13 @@
         <v>3302</v>
       </c>
       <c r="H43" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I43" t="str">
         <v>Y</v>
+      </c>
+      <c r="J43" t="str">
+        <v/>
       </c>
     </row>
     <row r="44">
@@ -2299,10 +2536,13 @@
         <v>4273</v>
       </c>
       <c r="H44" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I44" t="str">
         <v>Y</v>
+      </c>
+      <c r="J44" t="str">
+        <v/>
       </c>
     </row>
     <row r="45">
@@ -2328,10 +2568,13 @@
         <v>5244</v>
       </c>
       <c r="H45" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I45" t="str">
         <v>Y</v>
+      </c>
+      <c r="J45" t="str">
+        <v/>
       </c>
     </row>
     <row r="46">
@@ -2357,10 +2600,13 @@
         <v>6215</v>
       </c>
       <c r="H46" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I46" t="str">
         <v>Y</v>
+      </c>
+      <c r="J46" t="str">
+        <v/>
       </c>
     </row>
     <row r="47">
@@ -2386,10 +2632,13 @@
         <v>7186</v>
       </c>
       <c r="H47" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I47" t="str">
         <v>Y</v>
+      </c>
+      <c r="J47" t="str">
+        <v/>
       </c>
     </row>
     <row r="48">
@@ -2415,10 +2664,13 @@
         <v>8157</v>
       </c>
       <c r="H48" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I48" t="str">
         <v>Y</v>
+      </c>
+      <c r="J48" t="str">
+        <v/>
       </c>
     </row>
     <row r="49">
@@ -2444,10 +2696,13 @@
         <v>9128</v>
       </c>
       <c r="H49" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I49" t="str">
         <v>Y</v>
+      </c>
+      <c r="J49" t="str">
+        <v/>
       </c>
     </row>
     <row r="50">
@@ -2473,10 +2728,13 @@
         <v>699</v>
       </c>
       <c r="H50" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I50" t="str">
         <v>Y</v>
+      </c>
+      <c r="J50" t="str">
+        <v/>
       </c>
     </row>
     <row r="51">
@@ -2502,10 +2760,13 @@
         <v>1670</v>
       </c>
       <c r="H51" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I51" t="str">
         <v>Y</v>
+      </c>
+      <c r="J51" t="str">
+        <v/>
       </c>
     </row>
     <row r="52">
@@ -2531,10 +2792,13 @@
         <v>2641</v>
       </c>
       <c r="H52" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I52" t="str">
         <v>Y</v>
+      </c>
+      <c r="J52" t="str">
+        <v/>
       </c>
     </row>
     <row r="53">
@@ -2560,10 +2824,13 @@
         <v>3612</v>
       </c>
       <c r="H53" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I53" t="str">
         <v>Y</v>
+      </c>
+      <c r="J53" t="str">
+        <v/>
       </c>
     </row>
     <row r="54">
@@ -2589,10 +2856,13 @@
         <v>4583</v>
       </c>
       <c r="H54" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I54" t="str">
         <v>Y</v>
+      </c>
+      <c r="J54" t="str">
+        <v/>
       </c>
     </row>
     <row r="55">
@@ -2618,10 +2888,13 @@
         <v>5554</v>
       </c>
       <c r="H55" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I55" t="str">
         <v>Y</v>
+      </c>
+      <c r="J55" t="str">
+        <v/>
       </c>
     </row>
     <row r="56">
@@ -2647,10 +2920,13 @@
         <v>6525</v>
       </c>
       <c r="H56" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I56" t="str">
         <v>Y</v>
+      </c>
+      <c r="J56" t="str">
+        <v/>
       </c>
     </row>
     <row r="57">
@@ -2676,10 +2952,13 @@
         <v>7496</v>
       </c>
       <c r="H57" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I57" t="str">
         <v>Y</v>
+      </c>
+      <c r="J57" t="str">
+        <v/>
       </c>
     </row>
     <row r="58">
@@ -2705,10 +2984,13 @@
         <v>8467</v>
       </c>
       <c r="H58" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I58" t="str">
         <v>Y</v>
+      </c>
+      <c r="J58" t="str">
+        <v/>
       </c>
     </row>
     <row r="59">
@@ -2734,10 +3016,13 @@
         <v>9438</v>
       </c>
       <c r="H59" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I59" t="str">
         <v>Y</v>
+      </c>
+      <c r="J59" t="str">
+        <v/>
       </c>
     </row>
     <row r="60">
@@ -2763,10 +3048,13 @@
         <v>1009</v>
       </c>
       <c r="H60" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I60" t="str">
         <v>Y</v>
+      </c>
+      <c r="J60" t="str">
+        <v/>
       </c>
     </row>
     <row r="61">
@@ -2792,10 +3080,13 @@
         <v>1980</v>
       </c>
       <c r="H61" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I61" t="str">
         <v>Y</v>
+      </c>
+      <c r="J61" t="str">
+        <v/>
       </c>
     </row>
     <row r="62">
@@ -2821,10 +3112,13 @@
         <v>2951</v>
       </c>
       <c r="H62" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I62" t="str">
         <v>Y</v>
+      </c>
+      <c r="J62" t="str">
+        <v/>
       </c>
     </row>
     <row r="63">
@@ -2850,10 +3144,13 @@
         <v>3922</v>
       </c>
       <c r="H63" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I63" t="str">
         <v>Y</v>
+      </c>
+      <c r="J63" t="str">
+        <v/>
       </c>
     </row>
     <row r="64">
@@ -2879,10 +3176,13 @@
         <v>4893</v>
       </c>
       <c r="H64" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I64" t="str">
         <v>Y</v>
+      </c>
+      <c r="J64" t="str">
+        <v/>
       </c>
     </row>
     <row r="65">
@@ -2908,10 +3208,13 @@
         <v>5864</v>
       </c>
       <c r="H65" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I65" t="str">
         <v>Y</v>
+      </c>
+      <c r="J65" t="str">
+        <v/>
       </c>
     </row>
     <row r="66">
@@ -2937,10 +3240,13 @@
         <v>6835</v>
       </c>
       <c r="H66" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I66" t="str">
         <v>Y</v>
+      </c>
+      <c r="J66" t="str">
+        <v/>
       </c>
     </row>
     <row r="67">
@@ -2966,10 +3272,13 @@
         <v>7806</v>
       </c>
       <c r="H67" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I67" t="str">
         <v>Y</v>
+      </c>
+      <c r="J67" t="str">
+        <v/>
       </c>
     </row>
     <row r="68">
@@ -2995,10 +3304,13 @@
         <v>8777</v>
       </c>
       <c r="H68" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I68" t="str">
         <v>Y</v>
+      </c>
+      <c r="J68" t="str">
+        <v/>
       </c>
     </row>
     <row r="69">
@@ -3024,10 +3336,13 @@
         <v>348</v>
       </c>
       <c r="H69" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I69" t="str">
         <v>Y</v>
+      </c>
+      <c r="J69" t="str">
+        <v/>
       </c>
     </row>
     <row r="70">
@@ -3053,10 +3368,13 @@
         <v>1319</v>
       </c>
       <c r="H70" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I70" t="str">
         <v>Y</v>
+      </c>
+      <c r="J70" t="str">
+        <v/>
       </c>
     </row>
     <row r="71">
@@ -3082,10 +3400,13 @@
         <v>2290</v>
       </c>
       <c r="H71" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I71" t="str">
         <v>Y</v>
+      </c>
+      <c r="J71" t="str">
+        <v/>
       </c>
     </row>
     <row r="72">
@@ -3111,10 +3432,13 @@
         <v>3261</v>
       </c>
       <c r="H72" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I72" t="str">
         <v>Y</v>
+      </c>
+      <c r="J72" t="str">
+        <v/>
       </c>
     </row>
     <row r="73">
@@ -3140,10 +3464,13 @@
         <v>4232</v>
       </c>
       <c r="H73" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I73" t="str">
         <v>Y</v>
+      </c>
+      <c r="J73" t="str">
+        <v/>
       </c>
     </row>
     <row r="74">
@@ -3169,10 +3496,13 @@
         <v>5203</v>
       </c>
       <c r="H74" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I74" t="str">
         <v>Y</v>
+      </c>
+      <c r="J74" t="str">
+        <v/>
       </c>
     </row>
     <row r="75">
@@ -3198,10 +3528,13 @@
         <v>6174</v>
       </c>
       <c r="H75" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I75" t="str">
         <v>Y</v>
+      </c>
+      <c r="J75" t="str">
+        <v/>
       </c>
     </row>
     <row r="76">
@@ -3227,10 +3560,13 @@
         <v>7145</v>
       </c>
       <c r="H76" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I76" t="str">
         <v>Y</v>
+      </c>
+      <c r="J76" t="str">
+        <v/>
       </c>
     </row>
     <row r="77">
@@ -3256,10 +3592,13 @@
         <v>8116</v>
       </c>
       <c r="H77" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I77" t="str">
         <v>Y</v>
+      </c>
+      <c r="J77" t="str">
+        <v/>
       </c>
     </row>
     <row r="78">
@@ -3285,10 +3624,13 @@
         <v>9087</v>
       </c>
       <c r="H78" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I78" t="str">
         <v>Y</v>
+      </c>
+      <c r="J78" t="str">
+        <v/>
       </c>
     </row>
     <row r="79">
@@ -3314,10 +3656,13 @@
         <v>658</v>
       </c>
       <c r="H79" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I79" t="str">
         <v>Y</v>
+      </c>
+      <c r="J79" t="str">
+        <v/>
       </c>
     </row>
     <row r="80">
@@ -3343,10 +3688,13 @@
         <v>1629</v>
       </c>
       <c r="H80" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I80" t="str">
         <v>Y</v>
+      </c>
+      <c r="J80" t="str">
+        <v/>
       </c>
     </row>
     <row r="81">
@@ -3372,10 +3720,13 @@
         <v>2600</v>
       </c>
       <c r="H81" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I81" t="str">
         <v>Y</v>
+      </c>
+      <c r="J81" t="str">
+        <v/>
       </c>
     </row>
     <row r="82">
@@ -3401,10 +3752,13 @@
         <v>3571</v>
       </c>
       <c r="H82" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I82" t="str">
         <v>Y</v>
+      </c>
+      <c r="J82" t="str">
+        <v/>
       </c>
     </row>
     <row r="83">
@@ -3430,10 +3784,13 @@
         <v>4542</v>
       </c>
       <c r="H83" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I83" t="str">
         <v>Y</v>
+      </c>
+      <c r="J83" t="str">
+        <v/>
       </c>
     </row>
     <row r="84">
@@ -3459,10 +3816,13 @@
         <v>5513</v>
       </c>
       <c r="H84" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I84" t="str">
         <v>Y</v>
+      </c>
+      <c r="J84" t="str">
+        <v/>
       </c>
     </row>
     <row r="85">
@@ -3488,10 +3848,13 @@
         <v>6484</v>
       </c>
       <c r="H85" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I85" t="str">
         <v>Y</v>
+      </c>
+      <c r="J85" t="str">
+        <v/>
       </c>
     </row>
     <row r="86">
@@ -3517,10 +3880,13 @@
         <v>7455</v>
       </c>
       <c r="H86" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I86" t="str">
         <v>Y</v>
+      </c>
+      <c r="J86" t="str">
+        <v/>
       </c>
     </row>
     <row r="87">
@@ -3546,10 +3912,13 @@
         <v>8426</v>
       </c>
       <c r="H87" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I87" t="str">
         <v>Y</v>
+      </c>
+      <c r="J87" t="str">
+        <v/>
       </c>
     </row>
     <row r="88">
@@ -3575,10 +3944,13 @@
         <v>9397</v>
       </c>
       <c r="H88" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I88" t="str">
         <v>Y</v>
+      </c>
+      <c r="J88" t="str">
+        <v/>
       </c>
     </row>
     <row r="89">
@@ -3604,10 +3976,13 @@
         <v>968</v>
       </c>
       <c r="H89" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I89" t="str">
         <v>Y</v>
+      </c>
+      <c r="J89" t="str">
+        <v/>
       </c>
     </row>
     <row r="90">
@@ -3633,10 +4008,13 @@
         <v>1939</v>
       </c>
       <c r="H90" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I90" t="str">
         <v>Y</v>
+      </c>
+      <c r="J90" t="str">
+        <v/>
       </c>
     </row>
     <row r="91">
@@ -3662,10 +4040,13 @@
         <v>2910</v>
       </c>
       <c r="H91" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I91" t="str">
         <v>Y</v>
+      </c>
+      <c r="J91" t="str">
+        <v/>
       </c>
     </row>
     <row r="92">
@@ -3691,10 +4072,13 @@
         <v>3881</v>
       </c>
       <c r="H92" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I92" t="str">
         <v>Y</v>
+      </c>
+      <c r="J92" t="str">
+        <v/>
       </c>
     </row>
     <row r="93">
@@ -3720,10 +4104,13 @@
         <v>4852</v>
       </c>
       <c r="H93" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I93" t="str">
         <v>Y</v>
+      </c>
+      <c r="J93" t="str">
+        <v/>
       </c>
     </row>
     <row r="94">
@@ -3749,10 +4136,13 @@
         <v>5823</v>
       </c>
       <c r="H94" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I94" t="str">
         <v>Y</v>
+      </c>
+      <c r="J94" t="str">
+        <v/>
       </c>
     </row>
     <row r="95">
@@ -3778,10 +4168,13 @@
         <v>6794</v>
       </c>
       <c r="H95" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I95" t="str">
         <v>Y</v>
+      </c>
+      <c r="J95" t="str">
+        <v/>
       </c>
     </row>
     <row r="96">
@@ -3807,10 +4200,13 @@
         <v>7765</v>
       </c>
       <c r="H96" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I96" t="str">
         <v>Y</v>
+      </c>
+      <c r="J96" t="str">
+        <v/>
       </c>
     </row>
     <row r="97">
@@ -3836,10 +4232,13 @@
         <v>8736</v>
       </c>
       <c r="H97" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I97" t="str">
         <v>Y</v>
+      </c>
+      <c r="J97" t="str">
+        <v/>
       </c>
     </row>
     <row r="98">
@@ -3865,10 +4264,13 @@
         <v>307</v>
       </c>
       <c r="H98" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I98" t="str">
         <v>Y</v>
+      </c>
+      <c r="J98" t="str">
+        <v/>
       </c>
     </row>
     <row r="99">
@@ -3894,10 +4296,13 @@
         <v>1278</v>
       </c>
       <c r="H99" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I99" t="str">
         <v>Y</v>
+      </c>
+      <c r="J99" t="str">
+        <v/>
       </c>
     </row>
     <row r="100">
@@ -3923,10 +4328,13 @@
         <v>2249</v>
       </c>
       <c r="H100" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I100" t="str">
         <v>Y</v>
+      </c>
+      <c r="J100" t="str">
+        <v/>
       </c>
     </row>
     <row r="101">
@@ -3952,10 +4360,13 @@
         <v>3220</v>
       </c>
       <c r="H101" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I101" t="str">
         <v>Y</v>
+      </c>
+      <c r="J101" t="str">
+        <v/>
       </c>
     </row>
     <row r="102">
@@ -3981,10 +4392,13 @@
         <v>4191</v>
       </c>
       <c r="H102" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I102" t="str">
         <v>Y</v>
+      </c>
+      <c r="J102" t="str">
+        <v/>
       </c>
     </row>
     <row r="103">
@@ -4010,10 +4424,13 @@
         <v>5162</v>
       </c>
       <c r="H103" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I103" t="str">
         <v>Y</v>
+      </c>
+      <c r="J103" t="str">
+        <v/>
       </c>
     </row>
     <row r="104">
@@ -4039,10 +4456,13 @@
         <v>6133</v>
       </c>
       <c r="H104" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I104" t="str">
         <v>Y</v>
+      </c>
+      <c r="J104" t="str">
+        <v/>
       </c>
     </row>
     <row r="105">
@@ -4068,22 +4488,89 @@
         <v>7104</v>
       </c>
       <c r="H105" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="I105" t="str">
         <v>Y</v>
+      </c>
+      <c r="J105" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>V0105</v>
+      </c>
+      <c r="B106" t="str">
+        <v>C4</v>
+      </c>
+      <c r="C106" t="str">
+        <v>S47</v>
+      </c>
+      <c r="D106" t="str">
+        <v>스마트점프 초급 10</v>
+      </c>
+      <c r="E106" t="str">
+        <v>file:clips/clip1</v>
+      </c>
+      <c r="F106" t="str">
+        <v>00:42</v>
+      </c>
+      <c r="G106">
+        <v>0</v>
+      </c>
+      <c r="H106" t="str">
+        <v>2026-09-10</v>
+      </c>
+      <c r="I106" t="str">
+        <v>Y</v>
+      </c>
+      <c r="J106" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>V0106</v>
+      </c>
+      <c r="B107" t="str">
+        <v>C4</v>
+      </c>
+      <c r="C107" t="str">
+        <v>S47</v>
+      </c>
+      <c r="D107" t="str">
+        <v>스마트점프 초급 20 · 창작(자유) 패턴 익히기 -2-</v>
+      </c>
+      <c r="E107" t="str">
+        <v>file:clips/clip2</v>
+      </c>
+      <c r="F107" t="str">
+        <v>00:38</v>
+      </c>
+      <c r="G107">
+        <v>0</v>
+      </c>
+      <c r="H107" t="str">
+        <v>2026-09-10</v>
+      </c>
+      <c r="I107" t="str">
+        <v>Y</v>
+      </c>
+      <c r="J107" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I105"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J107"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:N4"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
@@ -4093,6 +4580,12 @@
     <col min="6" max="6" width="12.83203125" customWidth="1"/>
     <col min="7" max="7" width="12.83203125" customWidth="1"/>
     <col min="8" max="8" width="12.83203125" customWidth="1"/>
+    <col min="9" max="9" width="12.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+    <col min="13" max="13" width="12.83203125" customWidth="1"/>
+    <col min="14" max="14" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4120,6 +4613,24 @@
       <c r="H1" t="str">
         <v>상태</v>
       </c>
+      <c r="I1" t="str">
+        <v>학교코드</v>
+      </c>
+      <c r="J1" t="str">
+        <v>좌석수</v>
+      </c>
+      <c r="K1" t="str">
+        <v>이용시작</v>
+      </c>
+      <c r="L1" t="str">
+        <v>이용종료</v>
+      </c>
+      <c r="M1" t="str">
+        <v>세션토큰</v>
+      </c>
+      <c r="N1" t="str">
+        <v>세션시각</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -4141,10 +4652,28 @@
         <v>관리자</v>
       </c>
       <c r="G2" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="H2" t="str">
         <v>정상</v>
+      </c>
+      <c r="I2" t="str">
+        <v>스마트점핑 본부</v>
+      </c>
+      <c r="J2">
+        <v>5</v>
+      </c>
+      <c r="K2" t="str">
+        <v>2026-09-10</v>
+      </c>
+      <c r="L2" t="str">
+        <v>2027-09-10</v>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -4167,10 +4696,28 @@
         <v>교사</v>
       </c>
       <c r="G3" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="H3" t="str">
         <v>정상</v>
+      </c>
+      <c r="I3" t="str">
+        <v>옥동초등학교</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3" t="str">
+        <v>2026-09-10</v>
+      </c>
+      <c r="L3" t="str">
+        <v>2027-09-10</v>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -4193,15 +4740,33 @@
         <v>학생</v>
       </c>
       <c r="G4" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="H4" t="str">
         <v>정상</v>
       </c>
+      <c r="I4" t="str">
+        <v>강동초등학교</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4" t="str">
+        <v>2026-09-10</v>
+      </c>
+      <c r="L4" t="str">
+        <v>2027-09-10</v>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N4"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4297,25 +4862,25 @@
         <v>2026-08</v>
       </c>
       <c r="D3" t="str">
-        <v>울산광역시 북구</v>
+        <v>부산광역시 해운대구</v>
       </c>
       <c r="E3" t="str">
-        <v>강동초등학교</v>
+        <v>해운대초등학교</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I3" t="str">
         <v/>
       </c>
       <c r="J3" t="str">
-        <v>1학기 기본과정</v>
+        <v>체력왕 도전</v>
       </c>
     </row>
     <row r="4">
@@ -4329,25 +4894,25 @@
         <v>2026-07</v>
       </c>
       <c r="D4" t="str">
-        <v>울산광역시 북구</v>
+        <v>서울특별시 강남구</v>
       </c>
       <c r="E4" t="str">
-        <v>강동초등학교</v>
+        <v>대치초등학교</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G4">
         <v>2</v>
       </c>
       <c r="H4">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I4" t="str">
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>리듬 점핑반</v>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -4393,16 +4958,16 @@
         <v>2026-07</v>
       </c>
       <c r="D6" t="str">
-        <v>부산광역시 해운대구</v>
+        <v>울산광역시 남구</v>
       </c>
       <c r="E6" t="str">
-        <v>해운대초등학교</v>
+        <v>옥동초등학교</v>
       </c>
       <c r="F6">
         <v>5</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H6">
         <v>18</v>
@@ -4425,16 +4990,16 @@
         <v>2026-08</v>
       </c>
       <c r="D7" t="str">
-        <v>서울특별시 강남구</v>
+        <v>울산광역시 남구</v>
       </c>
       <c r="E7" t="str">
-        <v>대치초등학교</v>
+        <v>옥동초등학교</v>
       </c>
       <c r="F7">
         <v>6</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H7">
         <v>22</v>
@@ -4485,7 +5050,7 @@
         <v>김민준</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-08-15</v>
+        <v>2026-09-03</v>
       </c>
       <c r="D2" t="str">
         <v>출</v>
@@ -4499,7 +5064,7 @@
         <v>이서연</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-08-15</v>
+        <v>2026-09-03</v>
       </c>
       <c r="D3" t="str">
         <v>출</v>
@@ -4513,7 +5078,7 @@
         <v>박지호</v>
       </c>
       <c r="C4" t="str">
-        <v>2026-08-15</v>
+        <v>2026-09-03</v>
       </c>
       <c r="D4" t="str">
         <v>출</v>
@@ -4527,7 +5092,7 @@
         <v>최수아</v>
       </c>
       <c r="C5" t="str">
-        <v>2026-08-15</v>
+        <v>2026-09-03</v>
       </c>
       <c r="D5" t="str">
         <v>결</v>
@@ -4541,7 +5106,7 @@
         <v>정예준</v>
       </c>
       <c r="C6" t="str">
-        <v>2026-08-15</v>
+        <v>2026-09-03</v>
       </c>
       <c r="D6" t="str">
         <v>출</v>
@@ -4555,7 +5120,7 @@
         <v>강하윤</v>
       </c>
       <c r="C7" t="str">
-        <v>2026-08-15</v>
+        <v>2026-09-03</v>
       </c>
       <c r="D7" t="str">
         <v>출</v>
@@ -4569,7 +5134,7 @@
         <v>조은우</v>
       </c>
       <c r="C8" t="str">
-        <v>2026-08-15</v>
+        <v>2026-09-03</v>
       </c>
       <c r="D8" t="str">
         <v>출</v>
@@ -4583,7 +5148,7 @@
         <v>윤채원</v>
       </c>
       <c r="C9" t="str">
-        <v>2026-08-15</v>
+        <v>2026-09-03</v>
       </c>
       <c r="D9" t="str">
         <v>출</v>
@@ -4597,7 +5162,7 @@
         <v>학생</v>
       </c>
       <c r="C10" t="str">
-        <v>2026-08-15</v>
+        <v>2026-09-03</v>
       </c>
       <c r="D10" t="str">
         <v>출</v>
@@ -4611,7 +5176,7 @@
         <v>김민준</v>
       </c>
       <c r="C11" t="str">
-        <v>2026-08-19</v>
+        <v>2026-09-07</v>
       </c>
       <c r="D11" t="str">
         <v>출</v>
@@ -4625,7 +5190,7 @@
         <v>이서연</v>
       </c>
       <c r="C12" t="str">
-        <v>2026-08-19</v>
+        <v>2026-09-07</v>
       </c>
       <c r="D12" t="str">
         <v>출</v>
@@ -4639,7 +5204,7 @@
         <v>박지호</v>
       </c>
       <c r="C13" t="str">
-        <v>2026-08-19</v>
+        <v>2026-09-07</v>
       </c>
       <c r="D13" t="str">
         <v>결</v>
@@ -4653,7 +5218,7 @@
         <v>최수아</v>
       </c>
       <c r="C14" t="str">
-        <v>2026-08-19</v>
+        <v>2026-09-07</v>
       </c>
       <c r="D14" t="str">
         <v>출</v>
@@ -4667,7 +5232,7 @@
         <v>정예준</v>
       </c>
       <c r="C15" t="str">
-        <v>2026-08-19</v>
+        <v>2026-09-07</v>
       </c>
       <c r="D15" t="str">
         <v>지</v>
@@ -4681,7 +5246,7 @@
         <v>강하윤</v>
       </c>
       <c r="C16" t="str">
-        <v>2026-08-19</v>
+        <v>2026-09-07</v>
       </c>
       <c r="D16" t="str">
         <v>출</v>
@@ -4695,7 +5260,7 @@
         <v>조은우</v>
       </c>
       <c r="C17" t="str">
-        <v>2026-08-19</v>
+        <v>2026-09-07</v>
       </c>
       <c r="D17" t="str">
         <v>출</v>
@@ -4709,7 +5274,7 @@
         <v>윤채원</v>
       </c>
       <c r="C18" t="str">
-        <v>2026-08-19</v>
+        <v>2026-09-07</v>
       </c>
       <c r="D18" t="str">
         <v>출</v>
@@ -4723,7 +5288,7 @@
         <v>학생</v>
       </c>
       <c r="C19" t="str">
-        <v>2026-08-19</v>
+        <v>2026-09-07</v>
       </c>
       <c r="D19" t="str">
         <v>출</v>
@@ -4737,7 +5302,7 @@
         <v>김민준</v>
       </c>
       <c r="C20" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="D20" t="str">
         <v>출</v>
@@ -4751,7 +5316,7 @@
         <v>이서연</v>
       </c>
       <c r="C21" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="D21" t="str">
         <v>결</v>
@@ -4765,7 +5330,7 @@
         <v>박지호</v>
       </c>
       <c r="C22" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="D22" t="str">
         <v>출</v>
@@ -4779,7 +5344,7 @@
         <v>최수아</v>
       </c>
       <c r="C23" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="D23" t="str">
         <v>지</v>
@@ -4793,7 +5358,7 @@
         <v>정예준</v>
       </c>
       <c r="C24" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="D24" t="str">
         <v>출</v>
@@ -4807,7 +5372,7 @@
         <v>강하윤</v>
       </c>
       <c r="C25" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="D25" t="str">
         <v>출</v>
@@ -4821,7 +5386,7 @@
         <v>조은우</v>
       </c>
       <c r="C26" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="D26" t="str">
         <v>출</v>
@@ -4835,7 +5400,7 @@
         <v>윤채원</v>
       </c>
       <c r="C27" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="D27" t="str">
         <v>출</v>
@@ -4849,7 +5414,7 @@
         <v>학생</v>
       </c>
       <c r="C28" t="str">
-        <v>2026-08-22</v>
+        <v>2026-09-10</v>
       </c>
       <c r="D28" t="str">
         <v>결</v>
@@ -4911,7 +5476,7 @@
         <v>5</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-08-22 17:23:49</v>
+        <v>2026-09-10 08:32:14</v>
       </c>
     </row>
     <row r="3">
@@ -4931,7 +5496,7 @@
         <v>3</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-08-22 17:23:49</v>
+        <v>2026-09-10 08:32:14</v>
       </c>
     </row>
     <row r="4">
@@ -4951,7 +5516,7 @@
         <v>2</v>
       </c>
       <c r="F4" t="str">
-        <v>2026-08-22 17:23:49</v>
+        <v>2026-09-10 08:32:14</v>
       </c>
     </row>
   </sheetData>
